--- a/companies/ashcombe-advisory/Finance/FY2020 Financial Summary.xlsx
+++ b/companies/ashcombe-advisory/Finance/FY2020 Financial Summary.xlsx
@@ -474,20 +474,20 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>859505</v>
+        <v>870116</v>
       </c>
       <c r="C4" s="3">
-        <v>791694</v>
+        <v>610642</v>
       </c>
       <c r="D4" s="3">
-        <v>767401</v>
+        <v>702887</v>
       </c>
       <c r="E4" s="3">
-        <v>742400</v>
+        <v>787355</v>
       </c>
       <c r="F4" s="4">
         <f>SUM(B4:E4)</f>
-        <v>3161000</v>
+        <v>2971000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>196550</v>
+        <v>46180</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>2541350</v>
+        <v>2390980</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>619650</v>
+        <v>580020</v>
       </c>
     </row>
   </sheetData>
